--- a/tests/fixtures/mistakes_seed7.xlsx
+++ b/tests/fixtures/mistakes_seed7.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cms89\AppData\Roaming\Claude\scratch-workspaces\a72c5ced-5896-445f-ba4c-143e77ffe85d\78e220c2-1d03-4db7-9c30-facaa620e845\scratch-2026-10-19-6e9fe4\v3\tests\fixtures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D7BF9FF3-8BCC-491E-B401-722BDA16373E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8ED26E99-C898-41E7-9F39-E70B4D51956B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Start Here" sheetId="1" r:id="rId1"/>
@@ -23,23 +23,24 @@
     <sheet name="_meta" sheetId="8" state="veryHidden" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="BackorderCost">Scenario!$F$18</definedName>
+    <definedName name="BackorderCost">Scenario!$F$19</definedName>
+    <definedName name="BeginBackorders">Scenario!$F$7</definedName>
     <definedName name="BeginInv">Scenario!$F$6</definedName>
-    <definedName name="BottlesPerHour">Scenario!$F$11</definedName>
-    <definedName name="DaysPerMonth">Scenario!$F$13</definedName>
-    <definedName name="EndTarget">Scenario!$F$8</definedName>
-    <definedName name="HireCost">Scenario!$F$15</definedName>
-    <definedName name="HoldCost">Scenario!$F$17</definedName>
-    <definedName name="HoursPerDay">Scenario!$F$12</definedName>
-    <definedName name="LaborCost">Scenario!$F$14</definedName>
-    <definedName name="LayoffCost">Scenario!$F$16</definedName>
-    <definedName name="MaxInventory">Scenario!$F$9</definedName>
-    <definedName name="OTCost">Scenario!$F$20</definedName>
-    <definedName name="OTLimitPct">Scenario!$F$19</definedName>
-    <definedName name="SafetyStock">Scenario!$F$7</definedName>
-    <definedName name="StartWorkers">Scenario!$F$10</definedName>
-    <definedName name="SubCapacity">Scenario!$F$22</definedName>
-    <definedName name="SubCost">Scenario!$F$21</definedName>
+    <definedName name="BottlesPerHour">Scenario!$F$12</definedName>
+    <definedName name="DaysPerMonth">Scenario!$F$14</definedName>
+    <definedName name="EndTarget">Scenario!$F$9</definedName>
+    <definedName name="HireCost">Scenario!$F$16</definedName>
+    <definedName name="HoldCost">Scenario!$F$18</definedName>
+    <definedName name="HoursPerDay">Scenario!$F$13</definedName>
+    <definedName name="LaborCost">Scenario!$F$15</definedName>
+    <definedName name="LayoffCost">Scenario!$F$17</definedName>
+    <definedName name="MaxInventory">Scenario!$F$10</definedName>
+    <definedName name="OTCost">Scenario!$F$21</definedName>
+    <definedName name="OTLimitPct">Scenario!$F$20</definedName>
+    <definedName name="SafetyStock">Scenario!$F$8</definedName>
+    <definedName name="StartWorkers">Scenario!$F$11</definedName>
+    <definedName name="SubCapacity">Scenario!$F$23</definedName>
+    <definedName name="SubCost">Scenario!$F$22</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -134,7 +135,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="286">
   <si>
     <t>Aggregate Anxiety: Aggregate Planning in Excel</t>
   </si>
@@ -208,10 +209,64 @@
     <t>Yearly totals row (row 14)</t>
   </si>
   <si>
-    <t>Your company's policy</t>
-  </si>
-  <si>
-    <t>Your company carries no safety stock: the chase plan uses up the beginning inventory in January and then ends each month with 0 bottles; the level plan aims to end December at 0.</t>
+    <t>Your company's planning policies (every plan must follow them)</t>
+  </si>
+  <si>
+    <t>Safety stock: NONE</t>
+  </si>
+  <si>
+    <t>• Your company does NOT keep safety stock, so EndTarget = 0. The SafetyStock figure on the Scenario sheet is not used by your plans.</t>
+  </si>
+  <si>
+    <t>• Chase plan: use up the beginning inventory, then aim to end every month with 0 bottles on the shelf.</t>
+  </si>
+  <si>
+    <t>• Level plan: one steady rate, chosen so that December ends with 0 bottles.</t>
+  </si>
+  <si>
+    <t>• Hybrid plan: December may end with any stock of 0 or more.</t>
+  </si>
+  <si>
+    <t>• Beginning inventory (BeginInv = 2,400) is simply the stock on the shelf on January 1 — use it up; don't keep it as a reserve.</t>
+  </si>
+  <si>
+    <t>Backorders: unfilled orders carry forward</t>
+  </si>
+  <si>
+    <t>• An order you can't fill is not lost: it becomes a backorder and is still owed next month.</t>
+  </si>
+  <si>
+    <t>• You start the year owing BeginBackorders = 0 bottles of orders.</t>
+  </si>
+  <si>
+    <t>• When stock is available, old orders are shipped first, then this month's demand.</t>
+  </si>
+  <si>
+    <t>• Every bottle still on backorder at the end of a month costs BackorderCost for that month.</t>
+  </si>
+  <si>
+    <t>• Stock is never negative: a shortfall is recorded as backorders, not as negative inventory.</t>
+  </si>
+  <si>
+    <t>• Hybrid plan: no more than 0 bottles may still be on backorder at the end of December, and at least 95% of demand must ship in the month it is ordered.</t>
+  </si>
+  <si>
+    <t>Workforce: whole workers only</t>
+  </si>
+  <si>
+    <t>• You employ whole people — there are no fractions of a worker.</t>
+  </si>
+  <si>
+    <t>• If a month's production needs, say, 10.2 workers' worth of capacity, you must employ 11. The extra capacity sits idle, but those workers are still paid.</t>
+  </si>
+  <si>
+    <t>• Workers are paid LaborCost for every month they are employed, busy or not.</t>
+  </si>
+  <si>
+    <t>• You start the year with StartWorkers = 8 workers. Hiring and layoffs are counted against the previous month's workforce (January against StartWorkers): each hire costs HireCost, each layoff LayoffCost.</t>
+  </si>
+  <si>
+    <t>• One worker's monthly capacity comes from their output per hour, paid hours per day and working days per month (Scenario sheet).</t>
   </si>
   <si>
     <t>Questions every plan must answer, for each month</t>
@@ -352,22 +407,31 @@
     <t>February</t>
   </si>
   <si>
-    <t>Safety-stock quantity</t>
+    <t>Customer orders still unfilled before January</t>
+  </si>
+  <si>
+    <t>BeginBackorders</t>
+  </si>
+  <si>
+    <t>March</t>
+  </si>
+  <si>
+    <t>Safety-stock quantity (see Planning policies below)</t>
   </si>
   <si>
     <t>SafetyStock</t>
   </si>
   <si>
-    <t>March</t>
-  </si>
-  <si>
-    <t>Inventory each chase month aims to end with (and the level plan's December target)</t>
+    <t>April</t>
+  </si>
+  <si>
+    <t>Ending-inventory target your policy sets (see below)</t>
   </si>
   <si>
     <t>EndTarget</t>
   </si>
   <si>
-    <t>April</t>
+    <t>May</t>
   </si>
   <si>
     <t>Storage capacity (most bottles you can hold)</t>
@@ -376,7 +440,7 @@
     <t>MaxInventory</t>
   </si>
   <si>
-    <t>May</t>
+    <t>June</t>
   </si>
   <si>
     <t>Workers employed before January</t>
@@ -388,7 +452,7 @@
     <t>workers</t>
   </si>
   <si>
-    <t>June</t>
+    <t>July</t>
   </si>
   <si>
     <t>Output of one worker per hour</t>
@@ -400,7 +464,7 @@
     <t>bottles/hour</t>
   </si>
   <si>
-    <t>July</t>
+    <t>August</t>
   </si>
   <si>
     <t>Paid hours per worker per day</t>
@@ -412,7 +476,7 @@
     <t>hours/day</t>
   </si>
   <si>
-    <t>August</t>
+    <t>September</t>
   </si>
   <si>
     <t>Working days per month</t>
@@ -424,7 +488,7 @@
     <t>days/month</t>
   </si>
   <si>
-    <t>September</t>
+    <t>October</t>
   </si>
   <si>
     <t>Regular labor cost per worker per month</t>
@@ -436,7 +500,7 @@
     <t>$/worker/month</t>
   </si>
   <si>
-    <t>October</t>
+    <t>November</t>
   </si>
   <si>
     <t>Cost to hire one worker</t>
@@ -448,7 +512,7 @@
     <t>$/worker</t>
   </si>
   <si>
-    <t>November</t>
+    <t>December</t>
   </si>
   <si>
     <t>Cost to lay off one worker</t>
@@ -457,9 +521,6 @@
     <t>LayoffCost</t>
   </si>
   <si>
-    <t>December</t>
-  </si>
-  <si>
     <t>Cost to hold one bottle for one month</t>
   </si>
   <si>
@@ -508,6 +569,9 @@
     <t>bottles/month</t>
   </si>
   <si>
+    <t>Planning policies — how your company handles safety stock, backorders and workers</t>
+  </si>
+  <si>
     <t>Demand</t>
   </si>
   <si>
@@ -898,7 +962,7 @@
     <t>model_version</t>
   </si>
   <si>
-    <t>5.0.0</t>
+    <t>5.1.0</t>
   </si>
   <si>
     <t>seed</t>
@@ -907,7 +971,7 @@
     <t>config_hash</t>
   </si>
   <si>
-    <t>fdf36332bcdfa8fc</t>
+    <t>b2308c1b38e5432c</t>
   </si>
   <si>
     <t>student_id</t>
@@ -922,13 +986,13 @@
     <t>created_utc</t>
   </si>
   <si>
-    <t>2026-10-19T18:53:50Z</t>
+    <t>2026-10-19T19:43:03Z</t>
   </si>
   <si>
     <t>workbook_id</t>
   </si>
   <si>
-    <t>37f0fdb5e0a0</t>
+    <t>2d7ec47b698f</t>
   </si>
 </sst>
 </file>
@@ -1135,7 +1199,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1208,6 +1272,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1542,7 +1607,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:D41"/>
+  <dimension ref="B1:D59"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -1594,7 +1659,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="7" t="s">
         <v>9</v>
       </c>
@@ -1603,7 +1668,7 @@
       </c>
       <c r="D9" s="37"/>
     </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="7" t="s">
         <v>11</v>
       </c>
@@ -1612,7 +1677,7 @@
       </c>
       <c r="D10" s="37"/>
     </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="7" t="s">
         <v>13</v>
       </c>
@@ -1621,7 +1686,7 @@
       </c>
       <c r="D11" s="37"/>
     </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="7" t="s">
         <v>15</v>
       </c>
@@ -1630,7 +1695,7 @@
       </c>
       <c r="D12" s="37"/>
     </row>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="7" t="s">
         <v>17</v>
       </c>
@@ -1673,149 +1738,262 @@
         <v>24</v>
       </c>
     </row>
-    <row r="22" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="38" t="s">
+    <row r="22" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C22" s="37"/>
+      <c r="C22" s="38" t="s">
+        <v>26</v>
+      </c>
       <c r="D22" s="37"/>
     </row>
-    <row r="24" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B24" s="6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B25" s="13" t="s">
+    <row r="23" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C23" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="C25" t="s">
+      <c r="D23" s="37"/>
+    </row>
+    <row r="24" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C24" s="38" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B26" s="13" t="s">
+      <c r="D24" s="37"/>
+    </row>
+    <row r="25" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C25" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="C26" t="s">
+      <c r="D25" s="37"/>
+    </row>
+    <row r="26" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C26" s="38" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B27" s="13" t="s">
+      <c r="D26" s="37"/>
+    </row>
+    <row r="28" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C28" s="38" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B28" s="13" t="s">
+      <c r="D28" s="37"/>
+    </row>
+    <row r="29" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C29" s="38" t="s">
         <v>33</v>
       </c>
-      <c r="C28" t="s">
+      <c r="D29" s="37"/>
+    </row>
+    <row r="30" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C30" s="38" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B29" s="13" t="s">
+      <c r="D30" s="37"/>
+    </row>
+    <row r="31" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C31" s="38" t="s">
         <v>35</v>
       </c>
-      <c r="C29" t="s">
+      <c r="D31" s="37"/>
+    </row>
+    <row r="32" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C32" s="38" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B30" s="13" t="s">
+      <c r="D32" s="37"/>
+    </row>
+    <row r="33" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C33" s="38" t="s">
         <v>37</v>
       </c>
-      <c r="C30" t="s">
+      <c r="D33" s="37"/>
+    </row>
+    <row r="35" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="7" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B31" s="13" t="s">
+      <c r="C35" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="C31" t="s">
+      <c r="D35" s="37"/>
+    </row>
+    <row r="36" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C36" s="38" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B32" s="13" t="s">
+      <c r="D36" s="37"/>
+    </row>
+    <row r="37" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C37" s="38" t="s">
         <v>41</v>
       </c>
-      <c r="C32" t="s">
+      <c r="D37" s="37"/>
+    </row>
+    <row r="38" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C38" s="38" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="33" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B33" s="13" t="s">
+      <c r="D38" s="37"/>
+    </row>
+    <row r="39" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C39" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="C33" t="s">
+      <c r="D39" s="37"/>
+    </row>
+    <row r="42" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B42" s="6" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="34" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B34" s="13" t="s">
+    <row r="43" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B43" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C43" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="35" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B35" s="13" t="s">
+    <row r="44" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B44" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C44" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="36" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B36" s="13" t="s">
+    <row r="45" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B45" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C45" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="37" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B37" s="13" t="s">
+    <row r="46" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B46" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C46" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="38" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B38" s="13" t="s">
+    <row r="47" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B47" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C47" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="40" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B40" s="2" t="s">
+    <row r="48" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B48" s="13" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="41" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B41" s="2" t="s">
+      <c r="C48" t="s">
         <v>56</v>
+      </c>
+    </row>
+    <row r="49" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B49" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="C49" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="50" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B50" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="C50" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="51" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B51" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="C51" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="52" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B52" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="C52" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="53" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B53" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="C53" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="54" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B54" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="C54" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="55" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B55" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="C55" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="56" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B56" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C56" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="58" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B58" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="59" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B59" s="2" t="s">
+        <v>74</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection sheet="1" formatCells="0" formatColumns="0" formatRows="0"/>
-  <mergeCells count="7">
+  <mergeCells count="22">
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C13:D13"/>
     <mergeCell ref="D4:D6"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C26:D26"/>
     <mergeCell ref="C9:D9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1824,7 +2002,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H47"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -1838,354 +2016,622 @@
   <sheetData>
     <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>60</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="F5" s="14" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="G5" s="14" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="H5" s="14" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="B6" s="15">
         <v>7000</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="F6" s="15">
         <v>2400</v>
       </c>
       <c r="G6" s="17" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="B7" s="15">
         <v>6000</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="F7" s="15">
-        <v>2400</v>
+        <v>0</v>
       </c>
       <c r="G7" s="17" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="B8" s="15">
         <v>7000</v>
       </c>
       <c r="E8" s="16" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="F8" s="15">
-        <v>0</v>
+        <v>2400</v>
       </c>
       <c r="G8" s="17" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="H8" s="16" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="B9" s="15">
         <v>11500</v>
       </c>
       <c r="E9" s="16" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="F9" s="15">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="G9" s="17" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="B10" s="15">
         <v>13000</v>
       </c>
       <c r="E10" s="16" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="F10" s="15">
-        <v>8</v>
+        <v>30000</v>
       </c>
       <c r="G10" s="17" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="H10" s="16" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
       <c r="B11" s="15">
         <v>16500</v>
       </c>
       <c r="E11" s="16" t="s">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="F11" s="15">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G11" s="17" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="H11" s="16" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="B12" s="15">
         <v>18500</v>
       </c>
       <c r="E12" s="16" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="F12" s="15">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G12" s="17" t="s">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="H12" s="16" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="B13" s="15">
         <v>14000</v>
       </c>
       <c r="E13" s="16" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="F13" s="15">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="G13" s="17" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="H13" s="16" t="s">
-        <v>95</v>
+        <v>112</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="B14" s="15">
         <v>10500</v>
       </c>
       <c r="E14" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="F14" s="18">
-        <v>3200</v>
+        <v>114</v>
+      </c>
+      <c r="F14" s="15">
+        <v>25</v>
       </c>
       <c r="G14" s="17" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="H14" s="16" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="B15" s="15">
         <v>9000</v>
       </c>
       <c r="E15" s="16" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="F15" s="18">
-        <v>600</v>
+        <v>3200</v>
       </c>
       <c r="G15" s="17" t="s">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="H15" s="16" t="s">
-        <v>103</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="B16" s="15">
         <v>7000</v>
       </c>
       <c r="E16" s="16" t="s">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="F16" s="18">
-        <v>900</v>
+        <v>600</v>
       </c>
       <c r="G16" s="17" t="s">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="H16" s="16" t="s">
-        <v>103</v>
+        <v>124</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="B17" s="15">
         <v>6000</v>
       </c>
       <c r="E17" s="16" t="s">
-        <v>108</v>
+        <v>126</v>
       </c>
       <c r="F17" s="18">
-        <v>0.25</v>
+        <v>900</v>
       </c>
       <c r="G17" s="17" t="s">
-        <v>109</v>
+        <v>127</v>
       </c>
       <c r="H17" s="16" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="E18" s="16" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="F18" s="18">
-        <v>1.5</v>
+        <v>0.25</v>
       </c>
       <c r="G18" s="17" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="H18" s="16" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="E19" s="16" t="s">
-        <v>113</v>
-      </c>
-      <c r="F19" s="19">
-        <v>0.2</v>
+        <v>131</v>
+      </c>
+      <c r="F19" s="18">
+        <v>1.5</v>
       </c>
       <c r="G19" s="17" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="H19" s="16" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="E20" s="16" t="s">
-        <v>116</v>
-      </c>
-      <c r="F20" s="18">
-        <v>4.5</v>
+        <v>133</v>
+      </c>
+      <c r="F20" s="19">
+        <v>0.2</v>
       </c>
       <c r="G20" s="17" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="H20" s="16" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="E21" s="16" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="F21" s="18">
-        <v>5.25</v>
+        <v>4.5</v>
       </c>
       <c r="G21" s="17" t="s">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="H21" s="16" t="s">
-        <v>118</v>
+        <v>138</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="E22" s="16" t="s">
-        <v>121</v>
-      </c>
-      <c r="F22" s="15">
+        <v>139</v>
+      </c>
+      <c r="F22" s="18">
+        <v>5.25</v>
+      </c>
+      <c r="G22" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="H22" s="16" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E23" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="F23" s="15">
         <v>5000</v>
       </c>
-      <c r="G22" s="17" t="s">
-        <v>122</v>
-      </c>
-      <c r="H22" s="16" t="s">
-        <v>123</v>
-      </c>
+      <c r="G23" s="17" t="s">
+        <v>142</v>
+      </c>
+      <c r="H23" s="16" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A26" s="6" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="39" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27" s="37"/>
+      <c r="C27" s="37"/>
+      <c r="D27" s="37"/>
+      <c r="E27" s="37"/>
+      <c r="F27" s="37"/>
+      <c r="G27" s="37"/>
+      <c r="H27" s="37"/>
+    </row>
+    <row r="28" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="38" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28" s="37"/>
+      <c r="C28" s="37"/>
+      <c r="D28" s="37"/>
+      <c r="E28" s="37"/>
+      <c r="F28" s="37"/>
+      <c r="G28" s="37"/>
+      <c r="H28" s="37"/>
+    </row>
+    <row r="29" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="38" t="s">
+        <v>27</v>
+      </c>
+      <c r="B29" s="37"/>
+      <c r="C29" s="37"/>
+      <c r="D29" s="37"/>
+      <c r="E29" s="37"/>
+      <c r="F29" s="37"/>
+      <c r="G29" s="37"/>
+      <c r="H29" s="37"/>
+    </row>
+    <row r="30" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="38" t="s">
+        <v>28</v>
+      </c>
+      <c r="B30" s="37"/>
+      <c r="C30" s="37"/>
+      <c r="D30" s="37"/>
+      <c r="E30" s="37"/>
+      <c r="F30" s="37"/>
+      <c r="G30" s="37"/>
+      <c r="H30" s="37"/>
+    </row>
+    <row r="31" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="38" t="s">
+        <v>29</v>
+      </c>
+      <c r="B31" s="37"/>
+      <c r="C31" s="37"/>
+      <c r="D31" s="37"/>
+      <c r="E31" s="37"/>
+      <c r="F31" s="37"/>
+      <c r="G31" s="37"/>
+      <c r="H31" s="37"/>
+    </row>
+    <row r="32" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="B32" s="37"/>
+      <c r="C32" s="37"/>
+      <c r="D32" s="37"/>
+      <c r="E32" s="37"/>
+      <c r="F32" s="37"/>
+      <c r="G32" s="37"/>
+      <c r="H32" s="37"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="B34" s="37"/>
+      <c r="C34" s="37"/>
+      <c r="D34" s="37"/>
+      <c r="E34" s="37"/>
+      <c r="F34" s="37"/>
+      <c r="G34" s="37"/>
+      <c r="H34" s="37"/>
+    </row>
+    <row r="35" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="B35" s="37"/>
+      <c r="C35" s="37"/>
+      <c r="D35" s="37"/>
+      <c r="E35" s="37"/>
+      <c r="F35" s="37"/>
+      <c r="G35" s="37"/>
+      <c r="H35" s="37"/>
+    </row>
+    <row r="36" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="B36" s="37"/>
+      <c r="C36" s="37"/>
+      <c r="D36" s="37"/>
+      <c r="E36" s="37"/>
+      <c r="F36" s="37"/>
+      <c r="G36" s="37"/>
+      <c r="H36" s="37"/>
+    </row>
+    <row r="37" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="B37" s="37"/>
+      <c r="C37" s="37"/>
+      <c r="D37" s="37"/>
+      <c r="E37" s="37"/>
+      <c r="F37" s="37"/>
+      <c r="G37" s="37"/>
+      <c r="H37" s="37"/>
+    </row>
+    <row r="38" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="B38" s="37"/>
+      <c r="C38" s="37"/>
+      <c r="D38" s="37"/>
+      <c r="E38" s="37"/>
+      <c r="F38" s="37"/>
+      <c r="G38" s="37"/>
+      <c r="H38" s="37"/>
+    </row>
+    <row r="39" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="B39" s="37"/>
+      <c r="C39" s="37"/>
+      <c r="D39" s="37"/>
+      <c r="E39" s="37"/>
+      <c r="F39" s="37"/>
+      <c r="G39" s="37"/>
+      <c r="H39" s="37"/>
+    </row>
+    <row r="40" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="B40" s="37"/>
+      <c r="C40" s="37"/>
+      <c r="D40" s="37"/>
+      <c r="E40" s="37"/>
+      <c r="F40" s="37"/>
+      <c r="G40" s="37"/>
+      <c r="H40" s="37"/>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" s="39" t="s">
+        <v>38</v>
+      </c>
+      <c r="B42" s="37"/>
+      <c r="C42" s="37"/>
+      <c r="D42" s="37"/>
+      <c r="E42" s="37"/>
+      <c r="F42" s="37"/>
+      <c r="G42" s="37"/>
+      <c r="H42" s="37"/>
+    </row>
+    <row r="43" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="38" t="s">
+        <v>39</v>
+      </c>
+      <c r="B43" s="37"/>
+      <c r="C43" s="37"/>
+      <c r="D43" s="37"/>
+      <c r="E43" s="37"/>
+      <c r="F43" s="37"/>
+      <c r="G43" s="37"/>
+      <c r="H43" s="37"/>
+    </row>
+    <row r="44" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="B44" s="37"/>
+      <c r="C44" s="37"/>
+      <c r="D44" s="37"/>
+      <c r="E44" s="37"/>
+      <c r="F44" s="37"/>
+      <c r="G44" s="37"/>
+      <c r="H44" s="37"/>
+    </row>
+    <row r="45" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="B45" s="37"/>
+      <c r="C45" s="37"/>
+      <c r="D45" s="37"/>
+      <c r="E45" s="37"/>
+      <c r="F45" s="37"/>
+      <c r="G45" s="37"/>
+      <c r="H45" s="37"/>
+    </row>
+    <row r="46" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="38" t="s">
+        <v>42</v>
+      </c>
+      <c r="B46" s="37"/>
+      <c r="C46" s="37"/>
+      <c r="D46" s="37"/>
+      <c r="E46" s="37"/>
+      <c r="F46" s="37"/>
+      <c r="G46" s="37"/>
+      <c r="H46" s="37"/>
+    </row>
+    <row r="47" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="B47" s="37"/>
+      <c r="C47" s="37"/>
+      <c r="D47" s="37"/>
+      <c r="E47" s="37"/>
+      <c r="F47" s="37"/>
+      <c r="G47" s="37"/>
+      <c r="H47" s="37"/>
     </row>
   </sheetData>
   <sheetProtection sheet="1" formatCells="0" formatColumns="0" formatRows="0"/>
+  <mergeCells count="19">
+    <mergeCell ref="A27:H27"/>
+    <mergeCell ref="A42:H42"/>
+    <mergeCell ref="A47:H47"/>
+    <mergeCell ref="A32:H32"/>
+    <mergeCell ref="A29:H29"/>
+    <mergeCell ref="A35:H35"/>
+    <mergeCell ref="A34:H34"/>
+    <mergeCell ref="A43:H43"/>
+    <mergeCell ref="A38:H38"/>
+    <mergeCell ref="A28:H28"/>
+    <mergeCell ref="A44:H44"/>
+    <mergeCell ref="A31:H31"/>
+    <mergeCell ref="A40:H40"/>
+    <mergeCell ref="A30:H30"/>
+    <mergeCell ref="A39:H39"/>
+    <mergeCell ref="A36:H36"/>
+    <mergeCell ref="A45:H45"/>
+    <mergeCell ref="A46:H46"/>
+    <mergeCell ref="A37:H37"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2201,52 +2647,52 @@
   <sheetData>
     <row r="1" spans="1:30" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="20" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="C1" s="21" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="D1" s="21" t="s">
-        <v>126</v>
+        <v>147</v>
       </c>
       <c r="E1" s="21" t="s">
-        <v>127</v>
+        <v>148</v>
       </c>
       <c r="F1" s="21" t="s">
-        <v>128</v>
+        <v>149</v>
       </c>
       <c r="G1" s="21" t="s">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="H1" s="21" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="I1" s="21" t="s">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="J1" s="21" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="K1" s="21" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="L1" s="21" t="s">
-        <v>134</v>
+        <v>155</v>
       </c>
       <c r="M1" s="21" t="s">
-        <v>135</v>
+        <v>156</v>
       </c>
       <c r="N1" s="21" t="s">
-        <v>136</v>
+        <v>157</v>
       </c>
       <c r="O1" s="21" t="s">
-        <v>137</v>
+        <v>158</v>
       </c>
       <c r="P1" s="21" t="s">
-        <v>138</v>
+        <v>159</v>
       </c>
       <c r="Q1" s="21"/>
       <c r="R1" s="21"/>
@@ -2265,7 +2711,7 @@
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="B2" s="15">
         <v>7000</v>
@@ -2275,7 +2721,7 @@
         <v>2400</v>
       </c>
       <c r="D2" s="22">
-        <f>0</f>
+        <f>BeginBackorders</f>
         <v>0</v>
       </c>
       <c r="E2" s="22">
@@ -2343,7 +2789,7 @@
     </row>
     <row r="3" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="B3" s="15">
         <v>6000</v>
@@ -2420,7 +2866,7 @@
     </row>
     <row r="4" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="B4" s="15">
         <v>7000</v>
@@ -2498,7 +2944,7 @@
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="B5" s="15">
         <v>11500</v>
@@ -2576,7 +3022,7 @@
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="B6" s="15">
         <v>13000</v>
@@ -2654,7 +3100,7 @@
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
       <c r="B7" s="15">
         <v>16500</v>
@@ -2732,7 +3178,7 @@
     </row>
     <row r="8" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="B8" s="15">
         <v>18500</v>
@@ -2810,7 +3256,7 @@
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="B9" s="15">
         <v>14000</v>
@@ -2888,7 +3334,7 @@
     </row>
     <row r="10" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="B10" s="15">
         <v>10500</v>
@@ -2966,7 +3412,7 @@
     </row>
     <row r="11" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="B11" s="15">
         <v>9000</v>
@@ -3044,7 +3490,7 @@
     </row>
     <row r="12" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="B12" s="15">
         <v>7000</v>
@@ -3122,7 +3568,7 @@
     </row>
     <row r="13" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="B13" s="15">
         <v>6000</v>
@@ -3200,7 +3646,7 @@
     </row>
     <row r="14" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A14" s="23" t="s">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="B14" s="24"/>
       <c r="C14" s="25"/>
@@ -3261,24 +3707,24 @@
     </row>
     <row r="16" spans="1:30" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>140</v>
+        <v>161</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="39" t="s">
-        <v>141</v>
-      </c>
-      <c r="B17" s="40"/>
+      <c r="A17" s="40" t="s">
+        <v>162</v>
+      </c>
+      <c r="B17" s="41"/>
       <c r="C17" s="22">
         <f>BottlesPerHour*HoursPerDay*DaysPerMonth</f>
         <v>1000</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="39" t="s">
-        <v>142</v>
-      </c>
-      <c r="B18" s="40"/>
+      <c r="A18" s="40" t="s">
+        <v>163</v>
+      </c>
+      <c r="B18" s="41"/>
       <c r="C18" s="22">
         <f>EndTarget</f>
         <v>0</v>
@@ -3286,12 +3732,12 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>143</v>
+        <v>164</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>144</v>
+        <v>165</v>
       </c>
     </row>
   </sheetData>
@@ -3316,52 +3762,52 @@
   <sheetData>
     <row r="1" spans="1:30" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="20" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="C1" s="21" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="D1" s="21" t="s">
-        <v>126</v>
+        <v>147</v>
       </c>
       <c r="E1" s="21" t="s">
-        <v>127</v>
+        <v>148</v>
       </c>
       <c r="F1" s="21" t="s">
-        <v>128</v>
+        <v>149</v>
       </c>
       <c r="G1" s="21" t="s">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="H1" s="21" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="I1" s="21" t="s">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="J1" s="21" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="K1" s="21" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="L1" s="21" t="s">
-        <v>134</v>
+        <v>155</v>
       </c>
       <c r="M1" s="21" t="s">
-        <v>135</v>
+        <v>156</v>
       </c>
       <c r="N1" s="21" t="s">
-        <v>136</v>
+        <v>157</v>
       </c>
       <c r="O1" s="21" t="s">
-        <v>137</v>
+        <v>158</v>
       </c>
       <c r="P1" s="21" t="s">
-        <v>138</v>
+        <v>159</v>
       </c>
       <c r="Q1" s="21"/>
       <c r="R1" s="21"/>
@@ -3380,7 +3826,7 @@
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="B2" s="15">
         <v>7000</v>
@@ -3390,7 +3836,7 @@
         <v>2400</v>
       </c>
       <c r="D2" s="22">
-        <f>0</f>
+        <f>BeginBackorders</f>
         <v>0</v>
       </c>
       <c r="E2" s="22">
@@ -3458,7 +3904,7 @@
     </row>
     <row r="3" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="B3" s="15">
         <v>6000</v>
@@ -3536,7 +3982,7 @@
     </row>
     <row r="4" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="B4" s="15">
         <v>7000</v>
@@ -3614,7 +4060,7 @@
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="B5" s="15">
         <v>11500</v>
@@ -3692,7 +4138,7 @@
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="B6" s="15">
         <v>13000</v>
@@ -3770,7 +4216,7 @@
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
       <c r="B7" s="15">
         <v>16500</v>
@@ -3848,7 +4294,7 @@
     </row>
     <row r="8" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="B8" s="15">
         <v>18500</v>
@@ -3926,7 +4372,7 @@
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="B9" s="15">
         <v>14000</v>
@@ -4004,7 +4450,7 @@
     </row>
     <row r="10" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="B10" s="15">
         <v>10500</v>
@@ -4082,7 +4528,7 @@
     </row>
     <row r="11" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="B11" s="15">
         <v>9000</v>
@@ -4160,7 +4606,7 @@
     </row>
     <row r="12" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="B12" s="15">
         <v>7000</v>
@@ -4238,7 +4684,7 @@
     </row>
     <row r="13" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="B13" s="15">
         <v>6000</v>
@@ -4316,7 +4762,7 @@
     </row>
     <row r="14" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A14" s="23" t="s">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="B14" s="24"/>
       <c r="C14" s="25"/>
@@ -4377,54 +4823,54 @@
     </row>
     <row r="16" spans="1:30" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>140</v>
+        <v>161</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="39" t="s">
-        <v>141</v>
-      </c>
-      <c r="B17" s="40"/>
+      <c r="A17" s="40" t="s">
+        <v>162</v>
+      </c>
+      <c r="B17" s="41"/>
       <c r="C17" s="22">
         <f>BottlesPerHour*HoursPerDay*DaysPerMonth</f>
         <v>1000</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="39" t="s">
-        <v>145</v>
-      </c>
-      <c r="B18" s="40"/>
+      <c r="A18" s="40" t="s">
+        <v>166</v>
+      </c>
+      <c r="B18" s="41"/>
       <c r="C18" s="22">
         <f>EndTarget</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="39" t="s">
-        <v>146</v>
-      </c>
-      <c r="B19" s="40"/>
+      <c r="A19" s="40" t="s">
+        <v>167</v>
+      </c>
+      <c r="B19" s="41"/>
       <c r="C19" s="22">
         <f>SUM(B2:B13)</f>
         <v>126000</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="39" t="s">
-        <v>147</v>
-      </c>
-      <c r="B20" s="40"/>
+      <c r="A20" s="40" t="s">
+        <v>168</v>
+      </c>
+      <c r="B20" s="41"/>
       <c r="C20" s="22">
-        <f>(C19+C18-BeginInv)/12</f>
+        <f>(C19+C18-BeginInv+BeginBackorders)/12</f>
         <v>10300</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="39" t="s">
-        <v>148</v>
-      </c>
-      <c r="B21" s="40"/>
+      <c r="A21" s="40" t="s">
+        <v>169</v>
+      </c>
+      <c r="B21" s="41"/>
       <c r="C21" s="22">
         <f>ROUNDUP(C20/C17,0)</f>
         <v>11</v>
@@ -4432,12 +4878,12 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>149</v>
+        <v>170</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>144</v>
+        <v>165</v>
       </c>
     </row>
   </sheetData>
@@ -4465,70 +4911,70 @@
   <sheetData>
     <row r="1" spans="1:30" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="20" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="C1" s="21" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="D1" s="21" t="s">
-        <v>126</v>
+        <v>147</v>
       </c>
       <c r="E1" s="21" t="s">
-        <v>128</v>
+        <v>149</v>
       </c>
       <c r="F1" s="21" t="s">
+        <v>171</v>
+      </c>
+      <c r="G1" s="21" t="s">
+        <v>172</v>
+      </c>
+      <c r="H1" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="I1" s="21" t="s">
+        <v>174</v>
+      </c>
+      <c r="J1" s="21" t="s">
+        <v>175</v>
+      </c>
+      <c r="K1" s="21" t="s">
         <v>150</v>
       </c>
-      <c r="G1" s="21" t="s">
+      <c r="L1" s="21" t="s">
         <v>151</v>
       </c>
-      <c r="H1" s="21" t="s">
+      <c r="M1" s="21" t="s">
         <v>152</v>
       </c>
-      <c r="I1" s="21" t="s">
+      <c r="N1" s="21" t="s">
         <v>153</v>
       </c>
-      <c r="J1" s="21" t="s">
+      <c r="O1" s="21" t="s">
         <v>154</v>
       </c>
-      <c r="K1" s="21" t="s">
-        <v>129</v>
-      </c>
-      <c r="L1" s="21" t="s">
-        <v>130</v>
-      </c>
-      <c r="M1" s="21" t="s">
-        <v>131</v>
-      </c>
-      <c r="N1" s="21" t="s">
-        <v>132</v>
-      </c>
-      <c r="O1" s="21" t="s">
-        <v>133</v>
-      </c>
       <c r="P1" s="21" t="s">
-        <v>134</v>
+        <v>155</v>
       </c>
       <c r="Q1" s="21" t="s">
-        <v>135</v>
+        <v>156</v>
       </c>
       <c r="R1" s="21" t="s">
-        <v>155</v>
+        <v>176</v>
       </c>
       <c r="S1" s="21" t="s">
-        <v>156</v>
+        <v>177</v>
       </c>
       <c r="T1" s="21" t="s">
-        <v>136</v>
+        <v>157</v>
       </c>
       <c r="U1" s="21" t="s">
-        <v>137</v>
+        <v>158</v>
       </c>
       <c r="V1" s="21" t="s">
-        <v>138</v>
+        <v>159</v>
       </c>
       <c r="W1" s="21"/>
       <c r="X1" s="21"/>
@@ -4541,7 +4987,7 @@
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="B2" s="15">
         <v>7000</v>
@@ -4551,7 +4997,7 @@
         <v>2400</v>
       </c>
       <c r="D2" s="22">
-        <f>0</f>
+        <f>BeginBackorders</f>
         <v>0</v>
       </c>
       <c r="E2" s="22">
@@ -4633,7 +5079,7 @@
     </row>
     <row r="3" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="B3" s="15">
         <v>6000</v>
@@ -4725,7 +5171,7 @@
     </row>
     <row r="4" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="B4" s="15">
         <v>7000</v>
@@ -4817,7 +5263,7 @@
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="B5" s="15">
         <v>11500</v>
@@ -4909,7 +5355,7 @@
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="B6" s="15">
         <v>13000</v>
@@ -5001,7 +5447,7 @@
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
       <c r="B7" s="15">
         <v>16500</v>
@@ -5093,7 +5539,7 @@
     </row>
     <row r="8" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="B8" s="15">
         <v>18500</v>
@@ -5185,7 +5631,7 @@
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="B9" s="15">
         <v>14000</v>
@@ -5277,7 +5723,7 @@
     </row>
     <row r="10" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="B10" s="15">
         <v>10500</v>
@@ -5369,7 +5815,7 @@
     </row>
     <row r="11" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="B11" s="15">
         <v>9000</v>
@@ -5461,7 +5907,7 @@
     </row>
     <row r="12" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="B12" s="15">
         <v>7000</v>
@@ -5553,7 +5999,7 @@
     </row>
     <row r="13" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="B13" s="15">
         <v>6000</v>
@@ -5645,7 +6091,7 @@
     </row>
     <row r="14" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A14" s="23" t="s">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="B14" s="24"/>
       <c r="C14" s="25"/>
@@ -5724,24 +6170,24 @@
     </row>
     <row r="16" spans="1:30" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>140</v>
+        <v>161</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="39" t="s">
-        <v>141</v>
-      </c>
-      <c r="B17" s="40"/>
+      <c r="A17" s="40" t="s">
+        <v>162</v>
+      </c>
+      <c r="B17" s="41"/>
       <c r="C17" s="22">
         <f>BottlesPerHour*HoursPerDay*DaysPerMonth</f>
         <v>1000</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="39" t="s">
-        <v>157</v>
-      </c>
-      <c r="B18" s="40"/>
+      <c r="A18" s="40" t="s">
+        <v>178</v>
+      </c>
+      <c r="B18" s="41"/>
       <c r="C18" s="22">
         <f>C17*OTLimitPct</f>
         <v>200</v>
@@ -5749,17 +6195,17 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>158</v>
+        <v>179</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>144</v>
+        <v>165</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>159</v>
+        <v>180</v>
       </c>
     </row>
   </sheetData>
@@ -5785,29 +6231,29 @@
   <sheetData>
     <row r="1" spans="1:5" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>160</v>
+        <v>181</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="20" t="s">
-        <v>161</v>
+        <v>182</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>162</v>
+        <v>183</v>
       </c>
       <c r="C3" s="20" t="s">
-        <v>163</v>
+        <v>184</v>
       </c>
       <c r="D3" s="20" t="s">
-        <v>164</v>
+        <v>185</v>
       </c>
       <c r="E3" s="20" t="s">
-        <v>165</v>
+        <v>186</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="16" t="s">
-        <v>166</v>
+        <v>187</v>
       </c>
       <c r="B4" s="26">
         <f>'Chase Plan'!K14</f>
@@ -5822,12 +6268,12 @@
         <v>422400</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>167</v>
+        <v>188</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
-        <v>168</v>
+        <v>189</v>
       </c>
       <c r="B5" s="26">
         <f>'Chase Plan'!L14</f>
@@ -5842,12 +6288,12 @@
         <v>1800</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>167</v>
+        <v>188</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="B6" s="26">
         <f>'Chase Plan'!M14</f>
@@ -5862,48 +6308,48 @@
         <v>0</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>167</v>
+        <v>188</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
-        <v>170</v>
+        <v>191</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>171</v>
+        <v>192</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>171</v>
+        <v>192</v>
       </c>
       <c r="D7" s="26">
         <f>'Hybrid Plan'!R14</f>
         <v>13500</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>172</v>
+        <v>193</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="16" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="B8" s="27" t="s">
-        <v>171</v>
+        <v>192</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>171</v>
+        <v>192</v>
       </c>
       <c r="D8" s="26">
         <f>'Hybrid Plan'!S14</f>
         <v>0</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>172</v>
+        <v>193</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="B9" s="26">
         <f>'Chase Plan'!N14</f>
@@ -5918,12 +6364,12 @@
         <v>23225</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>167</v>
+        <v>188</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
-        <v>175</v>
+        <v>196</v>
       </c>
       <c r="B10" s="26">
         <f>'Chase Plan'!O14</f>
@@ -5938,12 +6384,12 @@
         <v>150</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>167</v>
+        <v>188</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="28" t="s">
-        <v>176</v>
+        <v>197</v>
       </c>
       <c r="B11" s="29">
         <f>'Chase Plan'!P14</f>
@@ -5958,12 +6404,12 @@
         <v>461075</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>167</v>
+        <v>188</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="s">
-        <v>177</v>
+        <v>198</v>
       </c>
       <c r="B12" s="30">
         <f>'Chase Plan'!G14</f>
@@ -5978,12 +6424,12 @@
         <v>3</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>178</v>
+        <v>199</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="16" t="s">
-        <v>179</v>
+        <v>200</v>
       </c>
       <c r="B13" s="30">
         <f>'Chase Plan'!H14</f>
@@ -5998,12 +6444,12 @@
         <v>0</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>178</v>
+        <v>199</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
-        <v>180</v>
+        <v>201</v>
       </c>
       <c r="B14" s="30">
         <f>MAX('Chase Plan'!F2:F13)</f>
@@ -6018,12 +6464,12 @@
         <v>11</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>181</v>
+        <v>202</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="16" t="s">
-        <v>182</v>
+        <v>203</v>
       </c>
       <c r="B15" s="30">
         <f>MAX('Chase Plan'!I2:I13)</f>
@@ -6038,12 +6484,12 @@
         <v>15400</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>181</v>
+        <v>202</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="16" t="s">
-        <v>183</v>
+        <v>204</v>
       </c>
       <c r="B16" s="30">
         <f>COUNTIF('Chase Plan'!J2:J13,"&gt;0")</f>
@@ -6058,109 +6504,109 @@
         <v>1</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>184</v>
+        <v>205</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
-        <v>185</v>
+        <v>206</v>
       </c>
       <c r="B18" s="31" t="str">
         <f>IF(B11&lt;C11,"Chase","Level")</f>
         <v>Chase</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>186</v>
+        <v>207</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="28" t="s">
-        <v>187</v>
+        <v>208</v>
       </c>
       <c r="B19" s="26">
         <f>ABS(B11-C11)</f>
         <v>998893.5</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>188</v>
+        <v>209</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="28" t="s">
-        <v>189</v>
+        <v>210</v>
       </c>
       <c r="B21" s="31" t="s">
-        <v>162</v>
+        <v>183</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>190</v>
+        <v>211</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="32" t="s">
-        <v>191</v>
-      </c>
-      <c r="B22" s="41" t="s">
-        <v>192</v>
-      </c>
-      <c r="C22" s="42"/>
-      <c r="D22" s="42"/>
-      <c r="E22" s="43"/>
+        <v>212</v>
+      </c>
+      <c r="B22" s="42" t="s">
+        <v>213</v>
+      </c>
+      <c r="C22" s="43"/>
+      <c r="D22" s="43"/>
+      <c r="E22" s="44"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="36" t="s">
-        <v>193</v>
-      </c>
-      <c r="B23" s="44"/>
-      <c r="C23" s="45"/>
-      <c r="D23" s="45"/>
-      <c r="E23" s="46"/>
+        <v>214</v>
+      </c>
+      <c r="B23" s="45"/>
+      <c r="C23" s="46"/>
+      <c r="D23" s="46"/>
+      <c r="E23" s="47"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="37"/>
-      <c r="B24" s="44"/>
-      <c r="C24" s="45"/>
-      <c r="D24" s="45"/>
-      <c r="E24" s="46"/>
+      <c r="B24" s="45"/>
+      <c r="C24" s="46"/>
+      <c r="D24" s="46"/>
+      <c r="E24" s="47"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="37"/>
-      <c r="B25" s="44"/>
-      <c r="C25" s="45"/>
-      <c r="D25" s="45"/>
-      <c r="E25" s="46"/>
+      <c r="B25" s="45"/>
+      <c r="C25" s="46"/>
+      <c r="D25" s="46"/>
+      <c r="E25" s="47"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="37"/>
-      <c r="B26" s="44"/>
-      <c r="C26" s="45"/>
-      <c r="D26" s="45"/>
-      <c r="E26" s="46"/>
+      <c r="B26" s="45"/>
+      <c r="C26" s="46"/>
+      <c r="D26" s="46"/>
+      <c r="E26" s="47"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="37"/>
-      <c r="B27" s="44"/>
-      <c r="C27" s="45"/>
-      <c r="D27" s="45"/>
-      <c r="E27" s="46"/>
+      <c r="B27" s="45"/>
+      <c r="C27" s="46"/>
+      <c r="D27" s="46"/>
+      <c r="E27" s="47"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B28" s="44"/>
-      <c r="C28" s="45"/>
-      <c r="D28" s="45"/>
-      <c r="E28" s="46"/>
+      <c r="B28" s="45"/>
+      <c r="C28" s="46"/>
+      <c r="D28" s="46"/>
+      <c r="E28" s="47"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B29" s="44"/>
-      <c r="C29" s="45"/>
-      <c r="D29" s="45"/>
-      <c r="E29" s="46"/>
+      <c r="B29" s="45"/>
+      <c r="C29" s="46"/>
+      <c r="D29" s="46"/>
+      <c r="E29" s="47"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B30" s="47"/>
-      <c r="C30" s="48"/>
-      <c r="D30" s="48"/>
-      <c r="E30" s="49"/>
+      <c r="B30" s="48"/>
+      <c r="C30" s="49"/>
+      <c r="D30" s="49"/>
+      <c r="E30" s="50"/>
     </row>
   </sheetData>
   <sheetProtection sheet="1" formatCells="0" formatColumns="0" formatRows="0"/>
@@ -6188,215 +6634,215 @@
   <sheetData>
     <row r="1" spans="1:3" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>194</v>
+        <v>215</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>195</v>
+        <v>216</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>196</v>
+        <v>217</v>
       </c>
       <c r="B4" s="38" t="s">
-        <v>197</v>
+        <v>218</v>
       </c>
       <c r="C4" s="37"/>
     </row>
     <row r="5" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>198</v>
+        <v>219</v>
       </c>
       <c r="B5" s="38" t="s">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="C5" s="37"/>
     </row>
     <row r="6" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>200</v>
+        <v>221</v>
       </c>
       <c r="B6" s="38" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="C6" s="37"/>
     </row>
     <row r="7" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>202</v>
+        <v>223</v>
       </c>
       <c r="B7" s="38" t="s">
-        <v>203</v>
+        <v>224</v>
       </c>
       <c r="C7" s="37"/>
     </row>
     <row r="8" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>204</v>
+        <v>225</v>
       </c>
       <c r="B8" s="38" t="s">
-        <v>205</v>
+        <v>226</v>
       </c>
       <c r="C8" s="37"/>
     </row>
     <row r="9" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>206</v>
+        <v>227</v>
       </c>
       <c r="B9" s="38" t="s">
-        <v>207</v>
+        <v>228</v>
       </c>
       <c r="C9" s="37"/>
     </row>
     <row r="11" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>208</v>
+        <v>229</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>209</v>
+        <v>230</v>
       </c>
       <c r="B12" s="33" t="s">
-        <v>210</v>
+        <v>231</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>211</v>
+        <v>232</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>212</v>
+        <v>233</v>
       </c>
       <c r="B13" s="33" t="s">
-        <v>213</v>
+        <v>234</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>214</v>
+        <v>235</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>215</v>
+        <v>236</v>
       </c>
       <c r="B14" s="33" t="s">
-        <v>216</v>
+        <v>237</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>217</v>
+        <v>238</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>218</v>
+        <v>239</v>
       </c>
       <c r="B15" s="33" t="s">
-        <v>219</v>
+        <v>240</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>220</v>
+        <v>241</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>221</v>
+        <v>242</v>
       </c>
       <c r="B16" s="33" t="s">
-        <v>222</v>
+        <v>243</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>223</v>
+        <v>244</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>224</v>
+        <v>245</v>
       </c>
       <c r="B17" s="33" t="s">
-        <v>225</v>
+        <v>246</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>226</v>
+        <v>247</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>227</v>
+        <v>248</v>
       </c>
       <c r="B18" s="33" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>229</v>
+        <v>250</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>230</v>
+        <v>251</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="B21" s="38" t="s">
-        <v>232</v>
+        <v>253</v>
       </c>
       <c r="C21" s="37"/>
     </row>
     <row r="22" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
       <c r="B22" s="38" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="C22" s="37"/>
     </row>
     <row r="23" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="B23" s="38" t="s">
-        <v>236</v>
+        <v>257</v>
       </c>
       <c r="C23" s="37"/>
     </row>
     <row r="24" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>237</v>
+        <v>258</v>
       </c>
       <c r="B24" s="38" t="s">
-        <v>238</v>
+        <v>259</v>
       </c>
       <c r="C24" s="37"/>
     </row>
     <row r="25" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
       <c r="B25" s="38" t="s">
-        <v>240</v>
+        <v>261</v>
       </c>
       <c r="C25" s="37"/>
     </row>
     <row r="27" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>241</v>
+        <v>262</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="38" t="s">
-        <v>242</v>
+        <v>263</v>
       </c>
       <c r="B28" s="37"/>
       <c r="C28" s="37"/>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>243</v>
+        <v>264</v>
       </c>
       <c r="B30" s="34">
         <v>0.25</v>
@@ -6404,7 +6850,7 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>244</v>
+        <v>265</v>
       </c>
       <c r="B31" s="35">
         <v>1200</v>
@@ -6413,7 +6859,7 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>245</v>
+        <v>266</v>
       </c>
       <c r="B32" s="35">
         <v>850</v>
@@ -6422,7 +6868,7 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>246</v>
+        <v>267</v>
       </c>
       <c r="B33" s="35">
         <v>1500</v>
@@ -6431,7 +6877,7 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>247</v>
+        <v>268</v>
       </c>
       <c r="B34" s="35">
         <v>2300</v>
@@ -6440,7 +6886,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>248</v>
+        <v>269</v>
       </c>
       <c r="B35" s="35">
         <v>975</v>
@@ -6449,7 +6895,7 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>249</v>
+        <v>270</v>
       </c>
       <c r="B36" s="35">
         <v>1840</v>
@@ -6483,15 +6929,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>250</v>
+        <v>271</v>
       </c>
       <c r="B1" t="s">
-        <v>251</v>
+        <v>272</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>252</v>
+        <v>273</v>
       </c>
       <c r="B2">
         <v>2</v>
@@ -6499,15 +6945,15 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>253</v>
+        <v>274</v>
       </c>
       <c r="B3" t="s">
-        <v>254</v>
+        <v>275</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>255</v>
+        <v>276</v>
       </c>
       <c r="B4">
         <v>7</v>
@@ -6515,15 +6961,15 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>256</v>
+        <v>277</v>
       </c>
       <c r="B5" t="s">
-        <v>257</v>
+        <v>278</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>258</v>
+        <v>279</v>
       </c>
       <c r="B6" t="s">
         <v>6</v>
@@ -6531,7 +6977,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>259</v>
+        <v>280</v>
       </c>
       <c r="B7" t="s">
         <v>3</v>
@@ -6539,23 +6985,23 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>260</v>
+        <v>281</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>261</v>
+        <v>282</v>
       </c>
       <c r="B9" t="s">
-        <v>262</v>
+        <v>283</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>263</v>
+        <v>284</v>
       </c>
       <c r="B10" t="s">
-        <v>264</v>
+        <v>285</v>
       </c>
     </row>
   </sheetData>

--- a/tests/fixtures/mistakes_seed7.xlsx
+++ b/tests/fixtures/mistakes_seed7.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cms89\AppData\Roaming\Claude\scratch-workspaces\a72c5ced-5896-445f-ba4c-143e77ffe85d\78e220c2-1d03-4db7-9c30-facaa620e845\scratch-2026-10-19-6e9fe4\v3\tests\fixtures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8ED26E99-C898-41E7-9F39-E70B4D51956B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4FECEC27-E055-4397-AE2F-A00EC83D0DE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,24 +23,23 @@
     <sheet name="_meta" sheetId="8" state="veryHidden" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="BackorderCost">Scenario!$F$19</definedName>
+    <definedName name="BackorderCost">Scenario!$F$18</definedName>
     <definedName name="BeginBackorders">Scenario!$F$7</definedName>
     <definedName name="BeginInv">Scenario!$F$6</definedName>
-    <definedName name="BottlesPerHour">Scenario!$F$12</definedName>
-    <definedName name="DaysPerMonth">Scenario!$F$14</definedName>
-    <definedName name="EndTarget">Scenario!$F$9</definedName>
-    <definedName name="HireCost">Scenario!$F$16</definedName>
-    <definedName name="HoldCost">Scenario!$F$18</definedName>
-    <definedName name="HoursPerDay">Scenario!$F$13</definedName>
-    <definedName name="LaborCost">Scenario!$F$15</definedName>
-    <definedName name="LayoffCost">Scenario!$F$17</definedName>
-    <definedName name="MaxInventory">Scenario!$F$10</definedName>
-    <definedName name="OTCost">Scenario!$F$21</definedName>
-    <definedName name="OTLimitPct">Scenario!$F$20</definedName>
-    <definedName name="SafetyStock">Scenario!$F$8</definedName>
-    <definedName name="StartWorkers">Scenario!$F$11</definedName>
-    <definedName name="SubCapacity">Scenario!$F$23</definedName>
-    <definedName name="SubCost">Scenario!$F$22</definedName>
+    <definedName name="BottlesPerHour">Scenario!$F$11</definedName>
+    <definedName name="DaysPerMonth">Scenario!$F$13</definedName>
+    <definedName name="EndTarget">Scenario!$F$8</definedName>
+    <definedName name="HireCost">Scenario!$F$15</definedName>
+    <definedName name="HoldCost">Scenario!$F$17</definedName>
+    <definedName name="HoursPerDay">Scenario!$F$12</definedName>
+    <definedName name="LaborCost">Scenario!$F$14</definedName>
+    <definedName name="LayoffCost">Scenario!$F$16</definedName>
+    <definedName name="MaxInventory">Scenario!$F$9</definedName>
+    <definedName name="OTCost">Scenario!$F$20</definedName>
+    <definedName name="OTLimitPct">Scenario!$F$19</definedName>
+    <definedName name="StartWorkers">Scenario!$F$10</definedName>
+    <definedName name="SubCapacity">Scenario!$F$22</definedName>
+    <definedName name="SubCost">Scenario!$F$21</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -135,7 +134,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="288">
   <si>
     <t>Aggregate Anxiety: Aggregate Planning in Excel</t>
   </si>
@@ -215,7 +214,7 @@
     <t>Safety stock: NONE</t>
   </si>
   <si>
-    <t>• Your company does NOT keep safety stock, so EndTarget = 0. The SafetyStock figure on the Scenario sheet is not used by your plans.</t>
+    <t>• Your company does NOT keep safety stock, so EndTarget = 0.</t>
   </si>
   <si>
     <t>• Chase plan: use up the beginning inventory, then aim to end every month with 0 bottles on the shelf.</t>
@@ -416,111 +415,105 @@
     <t>March</t>
   </si>
   <si>
-    <t>Safety-stock quantity (see Planning policies below)</t>
-  </si>
-  <si>
-    <t>SafetyStock</t>
+    <t>Ending-inventory target your safety-stock policy sets (see below)</t>
+  </si>
+  <si>
+    <t>EndTarget</t>
   </si>
   <si>
     <t>April</t>
   </si>
   <si>
-    <t>Ending-inventory target your policy sets (see below)</t>
-  </si>
-  <si>
-    <t>EndTarget</t>
+    <t>Storage capacity (most bottles you can hold)</t>
+  </si>
+  <si>
+    <t>MaxInventory</t>
   </si>
   <si>
     <t>May</t>
   </si>
   <si>
-    <t>Storage capacity (most bottles you can hold)</t>
-  </si>
-  <si>
-    <t>MaxInventory</t>
+    <t>Workers employed before January</t>
+  </si>
+  <si>
+    <t>StartWorkers</t>
+  </si>
+  <si>
+    <t>workers</t>
   </si>
   <si>
     <t>June</t>
   </si>
   <si>
-    <t>Workers employed before January</t>
-  </si>
-  <si>
-    <t>StartWorkers</t>
-  </si>
-  <si>
-    <t>workers</t>
+    <t>Output of one worker per hour</t>
+  </si>
+  <si>
+    <t>BottlesPerHour</t>
+  </si>
+  <si>
+    <t>bottles/hour</t>
   </si>
   <si>
     <t>July</t>
   </si>
   <si>
-    <t>Output of one worker per hour</t>
-  </si>
-  <si>
-    <t>BottlesPerHour</t>
-  </si>
-  <si>
-    <t>bottles/hour</t>
+    <t>Paid hours per worker per day</t>
+  </si>
+  <si>
+    <t>HoursPerDay</t>
+  </si>
+  <si>
+    <t>hours/day</t>
   </si>
   <si>
     <t>August</t>
   </si>
   <si>
-    <t>Paid hours per worker per day</t>
-  </si>
-  <si>
-    <t>HoursPerDay</t>
-  </si>
-  <si>
-    <t>hours/day</t>
+    <t>Working days per month</t>
+  </si>
+  <si>
+    <t>DaysPerMonth</t>
+  </si>
+  <si>
+    <t>days/month</t>
   </si>
   <si>
     <t>September</t>
   </si>
   <si>
-    <t>Working days per month</t>
-  </si>
-  <si>
-    <t>DaysPerMonth</t>
-  </si>
-  <si>
-    <t>days/month</t>
+    <t>Regular labor cost per worker per month</t>
+  </si>
+  <si>
+    <t>LaborCost</t>
+  </si>
+  <si>
+    <t>$/worker/month</t>
   </si>
   <si>
     <t>October</t>
   </si>
   <si>
-    <t>Regular labor cost per worker per month</t>
-  </si>
-  <si>
-    <t>LaborCost</t>
-  </si>
-  <si>
-    <t>$/worker/month</t>
+    <t>Cost to hire one worker</t>
+  </si>
+  <si>
+    <t>HireCost</t>
+  </si>
+  <si>
+    <t>$/worker</t>
   </si>
   <si>
     <t>November</t>
   </si>
   <si>
-    <t>Cost to hire one worker</t>
-  </si>
-  <si>
-    <t>HireCost</t>
-  </si>
-  <si>
-    <t>$/worker</t>
+    <t>Cost to lay off one worker</t>
+  </si>
+  <si>
+    <t>LayoffCost</t>
   </si>
   <si>
     <t>December</t>
   </si>
   <si>
-    <t>Cost to lay off one worker</t>
-  </si>
-  <si>
-    <t>LayoffCost</t>
-  </si>
-  <si>
     <t>Cost to hold one bottle for one month</t>
   </si>
   <si>
@@ -986,13 +979,25 @@
     <t>created_utc</t>
   </si>
   <si>
-    <t>2026-10-19T19:43:03Z</t>
+    <t>2026-10-19T21:19:19Z</t>
   </si>
   <si>
     <t>workbook_id</t>
   </si>
   <si>
-    <t>2d7ec47b698f</t>
+    <t>68f32a977c1b</t>
+  </si>
+  <si>
+    <t>safety_stock_policy</t>
+  </si>
+  <si>
+    <t>none</t>
+  </si>
+  <si>
+    <t>worker_policy</t>
+  </si>
+  <si>
+    <t>whole</t>
   </si>
 </sst>
 </file>
@@ -1738,7 +1743,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="22" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="7" t="s">
         <v>25</v>
       </c>
@@ -2002,7 +2007,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H47"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -2103,7 +2108,7 @@
         <v>93</v>
       </c>
       <c r="F8" s="15">
-        <v>2400</v>
+        <v>0</v>
       </c>
       <c r="G8" s="17" t="s">
         <v>94</v>
@@ -2123,7 +2128,7 @@
         <v>96</v>
       </c>
       <c r="F9" s="15">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="G9" s="17" t="s">
         <v>97</v>
@@ -2143,133 +2148,133 @@
         <v>99</v>
       </c>
       <c r="F10" s="15">
-        <v>30000</v>
+        <v>8</v>
       </c>
       <c r="G10" s="17" t="s">
         <v>100</v>
       </c>
       <c r="H10" s="16" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B11" s="15">
         <v>16500</v>
       </c>
       <c r="E11" s="16" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F11" s="15">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G11" s="17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H11" s="16" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B12" s="15">
         <v>18500</v>
       </c>
       <c r="E12" s="16" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F12" s="15">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G12" s="17" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H12" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B13" s="15">
         <v>14000</v>
       </c>
       <c r="E13" s="16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F13" s="15">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="G13" s="17" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H13" s="16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B14" s="15">
         <v>10500</v>
       </c>
       <c r="E14" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="F14" s="15">
-        <v>25</v>
+        <v>115</v>
+      </c>
+      <c r="F14" s="18">
+        <v>3200</v>
       </c>
       <c r="G14" s="17" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H14" s="16" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B15" s="15">
         <v>9000</v>
       </c>
       <c r="E15" s="16" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F15" s="18">
-        <v>3200</v>
+        <v>600</v>
       </c>
       <c r="G15" s="17" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H15" s="16" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B16" s="15">
         <v>7000</v>
       </c>
       <c r="E16" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F16" s="18">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="G16" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H16" s="16" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -2283,107 +2288,105 @@
         <v>126</v>
       </c>
       <c r="F17" s="18">
-        <v>900</v>
+        <v>0.25</v>
       </c>
       <c r="G17" s="17" t="s">
         <v>127</v>
       </c>
       <c r="H17" s="16" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="E18" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="F18" s="18">
+        <v>1.5</v>
+      </c>
+      <c r="G18" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="H18" s="16" t="s">
         <v>128</v>
-      </c>
-      <c r="F18" s="18">
-        <v>0.25</v>
-      </c>
-      <c r="G18" s="17" t="s">
-        <v>129</v>
-      </c>
-      <c r="H18" s="16" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="E19" s="16" t="s">
         <v>131</v>
       </c>
-      <c r="F19" s="18">
-        <v>1.5</v>
+      <c r="F19" s="19">
+        <v>0.2</v>
       </c>
       <c r="G19" s="17" t="s">
         <v>132</v>
       </c>
       <c r="H19" s="16" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="E20" s="16" t="s">
-        <v>133</v>
-      </c>
-      <c r="F20" s="19">
-        <v>0.2</v>
+        <v>134</v>
+      </c>
+      <c r="F20" s="18">
+        <v>4.5</v>
       </c>
       <c r="G20" s="17" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H20" s="16" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="E21" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="F21" s="18">
+        <v>5.25</v>
+      </c>
+      <c r="G21" s="17" t="s">
+        <v>138</v>
+      </c>
+      <c r="H21" s="16" t="s">
         <v>136</v>
-      </c>
-      <c r="F21" s="18">
-        <v>4.5</v>
-      </c>
-      <c r="G21" s="17" t="s">
-        <v>137</v>
-      </c>
-      <c r="H21" s="16" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="E22" s="16" t="s">
         <v>139</v>
       </c>
-      <c r="F22" s="18">
-        <v>5.25</v>
+      <c r="F22" s="15">
+        <v>5000</v>
       </c>
       <c r="G22" s="17" t="s">
         <v>140</v>
       </c>
       <c r="H22" s="16" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="E23" s="16" t="s">
         <v>141</v>
       </c>
-      <c r="F23" s="15">
-        <v>5000</v>
-      </c>
-      <c r="G23" s="17" t="s">
+    </row>
+    <row r="25" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A25" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="H23" s="16" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A26" s="6" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="39" t="s">
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="39" t="s">
         <v>25</v>
+      </c>
+      <c r="B26" s="37"/>
+      <c r="C26" s="37"/>
+      <c r="D26" s="37"/>
+      <c r="E26" s="37"/>
+      <c r="F26" s="37"/>
+      <c r="G26" s="37"/>
+      <c r="H26" s="37"/>
+    </row>
+    <row r="27" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="38" t="s">
+        <v>26</v>
       </c>
       <c r="B27" s="37"/>
       <c r="C27" s="37"/>
@@ -2395,7 +2398,7 @@
     </row>
     <row r="28" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="38" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B28" s="37"/>
       <c r="C28" s="37"/>
@@ -2407,7 +2410,7 @@
     </row>
     <row r="29" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="38" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B29" s="37"/>
       <c r="C29" s="37"/>
@@ -2419,7 +2422,7 @@
     </row>
     <row r="30" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="38" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B30" s="37"/>
       <c r="C30" s="37"/>
@@ -2431,7 +2434,7 @@
     </row>
     <row r="31" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="38" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B31" s="37"/>
       <c r="C31" s="37"/>
@@ -2441,21 +2444,21 @@
       <c r="G31" s="37"/>
       <c r="H31" s="37"/>
     </row>
-    <row r="32" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="38" t="s">
-        <v>30</v>
-      </c>
-      <c r="B32" s="37"/>
-      <c r="C32" s="37"/>
-      <c r="D32" s="37"/>
-      <c r="E32" s="37"/>
-      <c r="F32" s="37"/>
-      <c r="G32" s="37"/>
-      <c r="H32" s="37"/>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="39" t="s">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" s="39" t="s">
         <v>31</v>
+      </c>
+      <c r="B33" s="37"/>
+      <c r="C33" s="37"/>
+      <c r="D33" s="37"/>
+      <c r="E33" s="37"/>
+      <c r="F33" s="37"/>
+      <c r="G33" s="37"/>
+      <c r="H33" s="37"/>
+    </row>
+    <row r="34" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="38" t="s">
+        <v>32</v>
       </c>
       <c r="B34" s="37"/>
       <c r="C34" s="37"/>
@@ -2467,7 +2470,7 @@
     </row>
     <row r="35" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="38" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B35" s="37"/>
       <c r="C35" s="37"/>
@@ -2479,7 +2482,7 @@
     </row>
     <row r="36" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="38" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B36" s="37"/>
       <c r="C36" s="37"/>
@@ -2491,7 +2494,7 @@
     </row>
     <row r="37" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="38" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B37" s="37"/>
       <c r="C37" s="37"/>
@@ -2503,7 +2506,7 @@
     </row>
     <row r="38" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="38" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B38" s="37"/>
       <c r="C38" s="37"/>
@@ -2513,9 +2516,9 @@
       <c r="G38" s="37"/>
       <c r="H38" s="37"/>
     </row>
-    <row r="39" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="38" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B39" s="37"/>
       <c r="C39" s="37"/>
@@ -2525,21 +2528,21 @@
       <c r="G39" s="37"/>
       <c r="H39" s="37"/>
     </row>
-    <row r="40" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="38" t="s">
-        <v>37</v>
-      </c>
-      <c r="B40" s="37"/>
-      <c r="C40" s="37"/>
-      <c r="D40" s="37"/>
-      <c r="E40" s="37"/>
-      <c r="F40" s="37"/>
-      <c r="G40" s="37"/>
-      <c r="H40" s="37"/>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="39" t="s">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" s="39" t="s">
         <v>38</v>
+      </c>
+      <c r="B41" s="37"/>
+      <c r="C41" s="37"/>
+      <c r="D41" s="37"/>
+      <c r="E41" s="37"/>
+      <c r="F41" s="37"/>
+      <c r="G41" s="37"/>
+      <c r="H41" s="37"/>
+    </row>
+    <row r="42" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="38" t="s">
+        <v>39</v>
       </c>
       <c r="B42" s="37"/>
       <c r="C42" s="37"/>
@@ -2549,9 +2552,9 @@
       <c r="G42" s="37"/>
       <c r="H42" s="37"/>
     </row>
-    <row r="43" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="38" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B43" s="37"/>
       <c r="C43" s="37"/>
@@ -2561,9 +2564,9 @@
       <c r="G43" s="37"/>
       <c r="H43" s="37"/>
     </row>
-    <row r="44" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="38" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B44" s="37"/>
       <c r="C44" s="37"/>
@@ -2573,9 +2576,9 @@
       <c r="G44" s="37"/>
       <c r="H44" s="37"/>
     </row>
-    <row r="45" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="38" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B45" s="37"/>
       <c r="C45" s="37"/>
@@ -2585,9 +2588,9 @@
       <c r="G45" s="37"/>
       <c r="H45" s="37"/>
     </row>
-    <row r="46" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="38" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B46" s="37"/>
       <c r="C46" s="37"/>
@@ -2597,40 +2600,28 @@
       <c r="G46" s="37"/>
       <c r="H46" s="37"/>
     </row>
-    <row r="47" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="38" t="s">
-        <v>43</v>
-      </c>
-      <c r="B47" s="37"/>
-      <c r="C47" s="37"/>
-      <c r="D47" s="37"/>
-      <c r="E47" s="37"/>
-      <c r="F47" s="37"/>
-      <c r="G47" s="37"/>
-      <c r="H47" s="37"/>
-    </row>
   </sheetData>
   <sheetProtection sheet="1" formatCells="0" formatColumns="0" formatRows="0"/>
   <mergeCells count="19">
+    <mergeCell ref="A46:H46"/>
+    <mergeCell ref="A37:H37"/>
     <mergeCell ref="A27:H27"/>
+    <mergeCell ref="A26:H26"/>
     <mergeCell ref="A42:H42"/>
-    <mergeCell ref="A47:H47"/>
-    <mergeCell ref="A32:H32"/>
+    <mergeCell ref="A33:H33"/>
     <mergeCell ref="A29:H29"/>
     <mergeCell ref="A35:H35"/>
-    <mergeCell ref="A34:H34"/>
     <mergeCell ref="A43:H43"/>
     <mergeCell ref="A38:H38"/>
     <mergeCell ref="A28:H28"/>
     <mergeCell ref="A44:H44"/>
     <mergeCell ref="A31:H31"/>
-    <mergeCell ref="A40:H40"/>
+    <mergeCell ref="A34:H34"/>
     <mergeCell ref="A30:H30"/>
     <mergeCell ref="A39:H39"/>
     <mergeCell ref="A36:H36"/>
     <mergeCell ref="A45:H45"/>
-    <mergeCell ref="A46:H46"/>
-    <mergeCell ref="A37:H37"/>
+    <mergeCell ref="A41:H41"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2650,49 +2641,49 @@
         <v>79</v>
       </c>
       <c r="B1" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="C1" s="21" t="s">
+        <v>144</v>
+      </c>
+      <c r="D1" s="21" t="s">
         <v>145</v>
       </c>
-      <c r="C1" s="21" t="s">
+      <c r="E1" s="21" t="s">
         <v>146</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="F1" s="21" t="s">
         <v>147</v>
       </c>
-      <c r="E1" s="21" t="s">
+      <c r="G1" s="21" t="s">
         <v>148</v>
       </c>
-      <c r="F1" s="21" t="s">
+      <c r="H1" s="21" t="s">
         <v>149</v>
       </c>
-      <c r="G1" s="21" t="s">
+      <c r="I1" s="21" t="s">
         <v>150</v>
       </c>
-      <c r="H1" s="21" t="s">
+      <c r="J1" s="21" t="s">
         <v>151</v>
       </c>
-      <c r="I1" s="21" t="s">
+      <c r="K1" s="21" t="s">
         <v>152</v>
       </c>
-      <c r="J1" s="21" t="s">
+      <c r="L1" s="21" t="s">
         <v>153</v>
       </c>
-      <c r="K1" s="21" t="s">
+      <c r="M1" s="21" t="s">
         <v>154</v>
       </c>
-      <c r="L1" s="21" t="s">
+      <c r="N1" s="21" t="s">
         <v>155</v>
       </c>
-      <c r="M1" s="21" t="s">
+      <c r="O1" s="21" t="s">
         <v>156</v>
       </c>
-      <c r="N1" s="21" t="s">
+      <c r="P1" s="21" t="s">
         <v>157</v>
-      </c>
-      <c r="O1" s="21" t="s">
-        <v>158</v>
-      </c>
-      <c r="P1" s="21" t="s">
-        <v>159</v>
       </c>
       <c r="Q1" s="21"/>
       <c r="R1" s="21"/>
@@ -3100,7 +3091,7 @@
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B7" s="15">
         <v>16500</v>
@@ -3178,7 +3169,7 @@
     </row>
     <row r="8" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B8" s="15">
         <v>18500</v>
@@ -3256,7 +3247,7 @@
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B9" s="15">
         <v>14000</v>
@@ -3334,7 +3325,7 @@
     </row>
     <row r="10" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B10" s="15">
         <v>10500</v>
@@ -3412,7 +3403,7 @@
     </row>
     <row r="11" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B11" s="15">
         <v>9000</v>
@@ -3490,7 +3481,7 @@
     </row>
     <row r="12" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B12" s="15">
         <v>7000</v>
@@ -3646,7 +3637,7 @@
     </row>
     <row r="14" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A14" s="23" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B14" s="24"/>
       <c r="C14" s="25"/>
@@ -3707,12 +3698,12 @@
     </row>
     <row r="16" spans="1:30" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="40" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B17" s="41"/>
       <c r="C17" s="22">
@@ -3722,7 +3713,7 @@
     </row>
     <row r="18" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="40" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B18" s="41"/>
       <c r="C18" s="22">
@@ -3732,12 +3723,12 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
   </sheetData>
@@ -3765,49 +3756,49 @@
         <v>79</v>
       </c>
       <c r="B1" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="C1" s="21" t="s">
+        <v>144</v>
+      </c>
+      <c r="D1" s="21" t="s">
         <v>145</v>
       </c>
-      <c r="C1" s="21" t="s">
+      <c r="E1" s="21" t="s">
         <v>146</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="F1" s="21" t="s">
         <v>147</v>
       </c>
-      <c r="E1" s="21" t="s">
+      <c r="G1" s="21" t="s">
         <v>148</v>
       </c>
-      <c r="F1" s="21" t="s">
+      <c r="H1" s="21" t="s">
         <v>149</v>
       </c>
-      <c r="G1" s="21" t="s">
+      <c r="I1" s="21" t="s">
         <v>150</v>
       </c>
-      <c r="H1" s="21" t="s">
+      <c r="J1" s="21" t="s">
         <v>151</v>
       </c>
-      <c r="I1" s="21" t="s">
+      <c r="K1" s="21" t="s">
         <v>152</v>
       </c>
-      <c r="J1" s="21" t="s">
+      <c r="L1" s="21" t="s">
         <v>153</v>
       </c>
-      <c r="K1" s="21" t="s">
+      <c r="M1" s="21" t="s">
         <v>154</v>
       </c>
-      <c r="L1" s="21" t="s">
+      <c r="N1" s="21" t="s">
         <v>155</v>
       </c>
-      <c r="M1" s="21" t="s">
+      <c r="O1" s="21" t="s">
         <v>156</v>
       </c>
-      <c r="N1" s="21" t="s">
+      <c r="P1" s="21" t="s">
         <v>157</v>
-      </c>
-      <c r="O1" s="21" t="s">
-        <v>158</v>
-      </c>
-      <c r="P1" s="21" t="s">
-        <v>159</v>
       </c>
       <c r="Q1" s="21"/>
       <c r="R1" s="21"/>
@@ -4216,7 +4207,7 @@
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B7" s="15">
         <v>16500</v>
@@ -4294,7 +4285,7 @@
     </row>
     <row r="8" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B8" s="15">
         <v>18500</v>
@@ -4372,7 +4363,7 @@
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B9" s="15">
         <v>14000</v>
@@ -4450,7 +4441,7 @@
     </row>
     <row r="10" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B10" s="15">
         <v>10500</v>
@@ -4528,7 +4519,7 @@
     </row>
     <row r="11" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B11" s="15">
         <v>9000</v>
@@ -4606,7 +4597,7 @@
     </row>
     <row r="12" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B12" s="15">
         <v>7000</v>
@@ -4762,7 +4753,7 @@
     </row>
     <row r="14" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A14" s="23" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B14" s="24"/>
       <c r="C14" s="25"/>
@@ -4823,12 +4814,12 @@
     </row>
     <row r="16" spans="1:30" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="40" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B17" s="41"/>
       <c r="C17" s="22">
@@ -4838,7 +4829,7 @@
     </row>
     <row r="18" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="40" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B18" s="41"/>
       <c r="C18" s="22">
@@ -4848,7 +4839,7 @@
     </row>
     <row r="19" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="40" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B19" s="41"/>
       <c r="C19" s="22">
@@ -4858,7 +4849,7 @@
     </row>
     <row r="20" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="40" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B20" s="41"/>
       <c r="C20" s="22">
@@ -4868,7 +4859,7 @@
     </row>
     <row r="21" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="40" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B21" s="41"/>
       <c r="C21" s="22">
@@ -4878,12 +4869,12 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
   </sheetData>
@@ -4914,67 +4905,67 @@
         <v>79</v>
       </c>
       <c r="B1" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="C1" s="21" t="s">
+        <v>144</v>
+      </c>
+      <c r="D1" s="21" t="s">
         <v>145</v>
       </c>
-      <c r="C1" s="21" t="s">
-        <v>146</v>
-      </c>
-      <c r="D1" s="21" t="s">
+      <c r="E1" s="21" t="s">
         <v>147</v>
       </c>
-      <c r="E1" s="21" t="s">
+      <c r="F1" s="21" t="s">
+        <v>169</v>
+      </c>
+      <c r="G1" s="21" t="s">
+        <v>170</v>
+      </c>
+      <c r="H1" s="21" t="s">
+        <v>171</v>
+      </c>
+      <c r="I1" s="21" t="s">
+        <v>172</v>
+      </c>
+      <c r="J1" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="K1" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="L1" s="21" t="s">
         <v>149</v>
       </c>
-      <c r="F1" s="21" t="s">
-        <v>171</v>
-      </c>
-      <c r="G1" s="21" t="s">
-        <v>172</v>
-      </c>
-      <c r="H1" s="21" t="s">
-        <v>173</v>
-      </c>
-      <c r="I1" s="21" t="s">
+      <c r="M1" s="21" t="s">
+        <v>150</v>
+      </c>
+      <c r="N1" s="21" t="s">
+        <v>151</v>
+      </c>
+      <c r="O1" s="21" t="s">
+        <v>152</v>
+      </c>
+      <c r="P1" s="21" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q1" s="21" t="s">
+        <v>154</v>
+      </c>
+      <c r="R1" s="21" t="s">
         <v>174</v>
       </c>
-      <c r="J1" s="21" t="s">
+      <c r="S1" s="21" t="s">
         <v>175</v>
       </c>
-      <c r="K1" s="21" t="s">
-        <v>150</v>
-      </c>
-      <c r="L1" s="21" t="s">
-        <v>151</v>
-      </c>
-      <c r="M1" s="21" t="s">
-        <v>152</v>
-      </c>
-      <c r="N1" s="21" t="s">
-        <v>153</v>
-      </c>
-      <c r="O1" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="P1" s="21" t="s">
+      <c r="T1" s="21" t="s">
         <v>155</v>
       </c>
-      <c r="Q1" s="21" t="s">
+      <c r="U1" s="21" t="s">
         <v>156</v>
       </c>
-      <c r="R1" s="21" t="s">
-        <v>176</v>
-      </c>
-      <c r="S1" s="21" t="s">
-        <v>177</v>
-      </c>
-      <c r="T1" s="21" t="s">
+      <c r="V1" s="21" t="s">
         <v>157</v>
-      </c>
-      <c r="U1" s="21" t="s">
-        <v>158</v>
-      </c>
-      <c r="V1" s="21" t="s">
-        <v>159</v>
       </c>
       <c r="W1" s="21"/>
       <c r="X1" s="21"/>
@@ -5447,7 +5438,7 @@
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B7" s="15">
         <v>16500</v>
@@ -5539,7 +5530,7 @@
     </row>
     <row r="8" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B8" s="15">
         <v>18500</v>
@@ -5631,7 +5622,7 @@
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B9" s="15">
         <v>14000</v>
@@ -5723,7 +5714,7 @@
     </row>
     <row r="10" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B10" s="15">
         <v>10500</v>
@@ -5815,7 +5806,7 @@
     </row>
     <row r="11" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B11" s="15">
         <v>9000</v>
@@ -5907,7 +5898,7 @@
     </row>
     <row r="12" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B12" s="15">
         <v>7000</v>
@@ -6091,7 +6082,7 @@
     </row>
     <row r="14" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A14" s="23" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B14" s="24"/>
       <c r="C14" s="25"/>
@@ -6170,12 +6161,12 @@
     </row>
     <row r="16" spans="1:30" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="40" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B17" s="41"/>
       <c r="C17" s="22">
@@ -6185,7 +6176,7 @@
     </row>
     <row r="18" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="40" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B18" s="41"/>
       <c r="C18" s="22">
@@ -6195,17 +6186,17 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
   </sheetData>
@@ -6231,29 +6222,29 @@
   <sheetData>
     <row r="1" spans="1:5" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="20" t="s">
+        <v>180</v>
+      </c>
+      <c r="B3" s="20" t="s">
+        <v>181</v>
+      </c>
+      <c r="C3" s="20" t="s">
         <v>182</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="D3" s="20" t="s">
         <v>183</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="E3" s="20" t="s">
         <v>184</v>
-      </c>
-      <c r="D3" s="20" t="s">
-        <v>185</v>
-      </c>
-      <c r="E3" s="20" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="16" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B4" s="26">
         <f>'Chase Plan'!K14</f>
@@ -6268,12 +6259,12 @@
         <v>422400</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B5" s="26">
         <f>'Chase Plan'!L14</f>
@@ -6288,12 +6279,12 @@
         <v>1800</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B6" s="26">
         <f>'Chase Plan'!M14</f>
@@ -6308,48 +6299,48 @@
         <v>0</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D7" s="26">
         <f>'Hybrid Plan'!R14</f>
         <v>13500</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="16" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B8" s="27" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D8" s="26">
         <f>'Hybrid Plan'!S14</f>
         <v>0</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B9" s="26">
         <f>'Chase Plan'!N14</f>
@@ -6364,12 +6355,12 @@
         <v>23225</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B10" s="26">
         <f>'Chase Plan'!O14</f>
@@ -6384,12 +6375,12 @@
         <v>150</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="28" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B11" s="29">
         <f>'Chase Plan'!P14</f>
@@ -6404,12 +6395,12 @@
         <v>461075</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B12" s="30">
         <f>'Chase Plan'!G14</f>
@@ -6424,12 +6415,12 @@
         <v>3</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="16" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B13" s="30">
         <f>'Chase Plan'!H14</f>
@@ -6444,12 +6435,12 @@
         <v>0</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B14" s="30">
         <f>MAX('Chase Plan'!F2:F13)</f>
@@ -6464,12 +6455,12 @@
         <v>11</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="16" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B15" s="30">
         <f>MAX('Chase Plan'!I2:I13)</f>
@@ -6484,12 +6475,12 @@
         <v>15400</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="16" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B16" s="30">
         <f>COUNTIF('Chase Plan'!J2:J13,"&gt;0")</f>
@@ -6504,50 +6495,50 @@
         <v>1</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B18" s="31" t="str">
         <f>IF(B11&lt;C11,"Chase","Level")</f>
         <v>Chase</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="28" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B19" s="26">
         <f>ABS(B11-C11)</f>
         <v>998893.5</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="28" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B21" s="31" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="32" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B22" s="42" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C22" s="43"/>
       <c r="D22" s="43"/>
@@ -6555,7 +6546,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="36" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B23" s="45"/>
       <c r="C23" s="46"/>
@@ -6634,215 +6625,215 @@
   <sheetData>
     <row r="1" spans="1:3" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B4" s="38" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C4" s="37"/>
     </row>
     <row r="5" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B5" s="38" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C5" s="37"/>
     </row>
     <row r="6" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B6" s="38" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C6" s="37"/>
     </row>
     <row r="7" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B7" s="38" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C7" s="37"/>
     </row>
     <row r="8" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B8" s="38" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C8" s="37"/>
     </row>
     <row r="9" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B9" s="38" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C9" s="37"/>
     </row>
     <row r="11" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="B12" s="33" t="s">
+        <v>229</v>
+      </c>
+      <c r="C12" s="8" t="s">
         <v>230</v>
-      </c>
-      <c r="B12" s="33" t="s">
-        <v>231</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B13" s="33" t="s">
+        <v>232</v>
+      </c>
+      <c r="C13" s="8" t="s">
         <v>233</v>
-      </c>
-      <c r="B13" s="33" t="s">
-        <v>234</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="B14" s="33" t="s">
+        <v>235</v>
+      </c>
+      <c r="C14" s="8" t="s">
         <v>236</v>
-      </c>
-      <c r="B14" s="33" t="s">
-        <v>237</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="B15" s="33" t="s">
+        <v>238</v>
+      </c>
+      <c r="C15" s="8" t="s">
         <v>239</v>
-      </c>
-      <c r="B15" s="33" t="s">
-        <v>240</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="B16" s="33" t="s">
+        <v>241</v>
+      </c>
+      <c r="C16" s="8" t="s">
         <v>242</v>
-      </c>
-      <c r="B16" s="33" t="s">
-        <v>243</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="B17" s="33" t="s">
+        <v>244</v>
+      </c>
+      <c r="C17" s="8" t="s">
         <v>245</v>
-      </c>
-      <c r="B17" s="33" t="s">
-        <v>246</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="B18" s="33" t="s">
+        <v>247</v>
+      </c>
+      <c r="C18" s="8" t="s">
         <v>248</v>
-      </c>
-      <c r="B18" s="33" t="s">
-        <v>249</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B21" s="38" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C21" s="37"/>
     </row>
     <row r="22" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B22" s="38" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C22" s="37"/>
     </row>
     <row r="23" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B23" s="38" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C23" s="37"/>
     </row>
     <row r="24" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B24" s="38" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C24" s="37"/>
     </row>
     <row r="25" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B25" s="38" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C25" s="37"/>
     </row>
     <row r="27" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="38" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B28" s="37"/>
       <c r="C28" s="37"/>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B30" s="34">
         <v>0.25</v>
@@ -6850,7 +6841,7 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B31" s="35">
         <v>1200</v>
@@ -6859,7 +6850,7 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B32" s="35">
         <v>850</v>
@@ -6868,7 +6859,7 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B33" s="35">
         <v>1500</v>
@@ -6877,7 +6868,7 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B34" s="35">
         <v>2300</v>
@@ -6886,7 +6877,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B35" s="35">
         <v>975</v>
@@ -6895,7 +6886,7 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B36" s="35">
         <v>1840</v>
@@ -6924,20 +6915,20 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B1" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B2">
         <v>2</v>
@@ -6945,15 +6936,15 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B3" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B4">
         <v>7</v>
@@ -6961,15 +6952,15 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B5" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B6" t="s">
         <v>6</v>
@@ -6977,7 +6968,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B7" t="s">
         <v>3</v>
@@ -6985,23 +6976,39 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B9" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>282</v>
+      </c>
+      <c r="B10" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>284</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B11" t="s">
         <v>285</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>286</v>
+      </c>
+      <c r="B12" t="s">
+        <v>287</v>
       </c>
     </row>
   </sheetData>
